--- a/web/files/九龙-尖沙咀-本木.xlsx
+++ b/web/files/九龙-尖沙咀-本木.xlsx
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>23000000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>32033</v>
+        <v>31900</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>19000000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>26462</v>
+        <v>26352</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>7408170</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>31391</v>
+        <v>31795</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>18406500</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>25636</v>
+        <v>25529</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>7176510</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>30409</v>
+        <v>30800</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>20395980</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>28407</v>
+        <v>28288</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>6970590</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>29536</v>
+        <v>29917</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>19427760</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>27058</v>
+        <v>26946</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>6701310</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>28395</v>
+        <v>28761</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>19127400</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>26640</v>
+        <v>26529</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>6736000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>28542</v>
+        <v>28910</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>19060000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>26546</v>
+        <v>26436</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>6512220</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>27594</v>
+        <v>27949</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>6467670</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>27405</v>
+        <v>27758</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>8308080</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>26543</v>
+        <v>26459</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>11600000</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>32584</v>
+        <v>32493</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
       <c r="F5" s="21" t="inlineStr"/>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>B1 | 236呎 (开放式)
+          <t>B1 | 233呎 (开放式)
 招标单位
 -
 (在售)</t>
@@ -8850,9 +8850,9 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>B2 | 718呎 (3房)
+          <t>B2 | 721呎 (3房)
 $2300万
-$32,033/呎
+$31,900/呎
 (23年-09月-05日)</t>
         </is>
       </c>
@@ -8915,17 +8915,17 @@
       <c r="F6" s="21" t="inlineStr"/>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>B1 | 236呎 (开放式)
+          <t>B1 | 233呎 (开放式)
 $741万
-$31,391/呎
+$31,795/呎
 (21年-09月-08日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>B2 | 718呎 (3房)
+          <t>B2 | 721呎 (3房)
 $1900万
-$26,462/呎
+$26,352/呎
 (24年-01月-28日)</t>
         </is>
       </c>
@@ -8988,17 +8988,17 @@
       <c r="F7" s="21" t="inlineStr"/>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>B1 | 236呎 (开放式)
+          <t>B1 | 233呎 (开放式)
 $718万
-$30,409/呎
+$30,800/呎
 (21年-08月-02日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>B2 | 718呎 (3房)
+          <t>B2 | 721呎 (3房)
 $1841万
-$25,636/呎
+$25,529/呎
 (24年-07月-10日)</t>
         </is>
       </c>
@@ -9134,17 +9134,17 @@
       <c r="F9" s="21" t="inlineStr"/>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>B1 | 236呎 (开放式)
+          <t>B1 | 233呎 (开放式)
 $697万
-$29,536/呎
+$29,917/呎
 (21年-07月-11日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>B2 | 718呎 (3房)
+          <t>B2 | 721呎 (3房)
 $2040万
-$28,407/呎
+$28,288/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -9207,17 +9207,17 @@
       <c r="F10" s="21" t="inlineStr"/>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>B1 | 236呎 (开放式)
+          <t>B1 | 233呎 (开放式)
 $670万
-$28,395/呎
+$28,761/呎
 (20年-12月-21日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>B2 | 718呎 (3房)
+          <t>B2 | 721呎 (3房)
 $1943万
-$27,058/呎
+$26,946/呎
 (20年-12月-21日)</t>
         </is>
       </c>
@@ -9280,17 +9280,17 @@
       <c r="F11" s="21" t="inlineStr"/>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>B1 | 236呎 (开放式)
+          <t>B1 | 233呎 (开放式)
 $674万
-$28,542/呎
+$28,910/呎
 (21年-05月-02日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>B2 | 718呎 (3房)
+          <t>B2 | 721呎 (3房)
 $1913万
-$26,640/呎
+$26,529/呎
 (23年-03月-28日)</t>
         </is>
       </c>
@@ -9353,17 +9353,17 @@
       <c r="F12" s="21" t="inlineStr"/>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>B1 | 236呎 (开放式)
+          <t>B1 | 233呎 (开放式)
 $651万
-$27,594/呎
+$27,949/呎
 (21年-01月-28日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>B2 | 718呎 (3房)
+          <t>B2 | 721呎 (3房)
 $1906万
-$26,546/呎
+$26,436/呎
 (23年-02月-14日)</t>
         </is>
       </c>
@@ -9426,9 +9426,9 @@
       <c r="F13" s="21" t="inlineStr"/>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>B1 | 236呎 (开放式)
+          <t>B1 | 233呎 (开放式)
 $647万
-$27,405/呎
+$27,758/呎
 (20年-12月-21日)</t>
         </is>
       </c>
@@ -10297,9 +10297,9 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>B2 | 356呎 (1房)
+          <t>B2 | 357呎 (1房)
 $1160万
-$32,584/呎
+$32,493/呎
 (22年-01月-26日)</t>
         </is>
       </c>
@@ -10321,9 +10321,9 @@
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
-          <t>B6 | 313呎 (1房)
+          <t>B6 | 314呎 (1房)
 $831万
-$26,543/呎
+$26,459/呎
 (21年-11月-29日)</t>
         </is>
       </c>
